--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rc382dcc49dac4850"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R2fcf8a20b0934c0c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -431,18 +431,18 @@
     </x:row>
     <x:row r="16" ht="33" customHeight="1">
       <x:c r="A16" s="5" t="str">
-        <x:v>输入保护</x:v>
+        <x:v>本地处理边界</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>邮件、发送记录、现有名单和策略文件保持不变，正式处理不连接外部邮件服务</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="33" customHeight="1">
+        <x:v>正式处理只读取邮件、发送记录、现有名单和策略文件，不连接外部邮件服务</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="48" customHeight="1">
       <x:c r="A17" s="5" t="str">
         <x:v>完成条件</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>npm run process:bounces返回0，六个目标路径可读，五份CSV以业务主键闭合</x:v>
+        <x:v>npm run process:bounces返回0，Prompt声明的目标路径可读，业务CSV以主键闭合</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="33" customHeight="1">

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R2fcf8a20b0934c0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R8b33030ba5c04c08"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -346,15 +346,15 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>脱敏营销邮件投递演练中的DSN邮件、发送记录、现有抑制名单和处置策略</x:v>
+        <x:v>本次营销邮件投递的DSN邮件、发送记录、现有抑制名单和处置策略，地址与消息标识已经脱敏</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="33" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>业务目标</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>解压输入数据包后在input_data目录读取mail、data、rules和starter</x:v>
+        <x:v>把退信邮件还原成可追溯处置，供投递运营更新抑制名单、安排重投并查看收件域退信情况</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="63" customHeight="1">
@@ -373,12 +373,12 @@
         <x:v>src/parse_bounces.mjs；reports/parsed_bounces.csv；reports/suppression_updates.csv；reports/retry_plan.csv；reports/bounce_exceptions.csv；reports/domain_summary.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="33" customHeight="1">
+    <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>软件步骤</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>解析MIME与DSN；关联发送记录；裁决重复和缺失；分类退信；生成抑制与重投；汇总收件域</x:v>
+        <x:v>用Node.js解析MIME与DSN，关联发送记录并裁决重复和缺失，再分类退信、生成抑制与重投安排并汇总收件域</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -431,34 +431,34 @@
     </x:row>
     <x:row r="16" ht="33" customHeight="1">
       <x:c r="A16" s="5" t="str">
-        <x:v>本地处理边界</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>正式处理只读取邮件、发送记录、现有名单和策略文件，不连接外部邮件服务</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="48" customHeight="1">
+        <x:v>只读取随包邮件、发送记录、现有名单和策略文件，不连接外部邮件服务</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="33" customHeight="1">
       <x:c r="A17" s="5" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>交付要求</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>npm run process:bounces返回0，Prompt声明的目标路径可读，业务CSV以主键闭合</x:v>
+        <x:v>交付完成版解析程序和五份CSV，退信、抑制、重投、异常与域级汇总以业务主键闭合</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="33" customHeight="1">
       <x:c r="A18" s="5" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>业务核对</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>DSN字段、字符解码、发送关联、重复键、异常原因、抑制范围、重投时间、尝试号和域级计数</x:v>
+        <x:v>核对DSN字段、字符解码、发送关联、重复键、异常原因、抑制范围、重投时间、尝试号和域级计数</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="33" customHeight="1">
       <x:c r="A19" s="5" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
+        <x:v>允许变体</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>函数拆分、变量名、注释、内部对象、临时对象名称、CSV必要引号和LF或CRLF行尾</x:v>
+        <x:v>函数拆分、变量名、注释和内部对象可以不同；CSV可使用必要引号以及LF或CRLF行尾</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
